--- a/research/traditional_assets/database/data/indonesia/indonesia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ18"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.039</v>
+        <v>0.06080000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.0237</v>
+        <v>0.0864</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>128.614</v>
+        <v>296.741</v>
       </c>
       <c r="L2">
-        <v>0.1337440193502162</v>
+        <v>0.2616482177402431</v>
       </c>
       <c r="M2">
-        <v>55.27</v>
+        <v>72.25</v>
       </c>
       <c r="N2">
-        <v>0.01874359896091212</v>
+        <v>0.02749552840887468</v>
       </c>
       <c r="O2">
-        <v>0.4297354875830002</v>
+        <v>0.2434783194772546</v>
       </c>
       <c r="P2">
-        <v>55.27</v>
+        <v>72.25</v>
       </c>
       <c r="Q2">
-        <v>0.01874359896091212</v>
+        <v>0.02749552840887468</v>
       </c>
       <c r="R2">
-        <v>0.4297354875830002</v>
+        <v>0.2434783194772546</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>441.554</v>
+        <v>518.79</v>
       </c>
       <c r="V2">
-        <v>0.1497432801806874</v>
+        <v>0.1974312136088595</v>
       </c>
       <c r="W2">
-        <v>0.03649643087739436</v>
+        <v>0.06070771298593879</v>
       </c>
       <c r="X2">
-        <v>0.03125859779739197</v>
+        <v>0.06277818877095842</v>
       </c>
       <c r="Y2">
-        <v>0.005237833080002391</v>
+        <v>-0.002070475785019635</v>
       </c>
       <c r="Z2">
-        <v>0.1613145541796232</v>
+        <v>0.2076414831110796</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03000222934004209</v>
+        <v>0.06437234203803117</v>
       </c>
       <c r="AC2">
-        <v>-0.03000222934004209</v>
+        <v>-0.06437234203803117</v>
       </c>
       <c r="AD2">
-        <v>3662.104</v>
+        <v>3686.398</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3662.104</v>
+        <v>3686.398</v>
       </c>
       <c r="AG2">
-        <v>3220.55</v>
+        <v>3167.608</v>
       </c>
       <c r="AH2">
-        <v>0.5539540790858172</v>
+        <v>0.5838360443566128</v>
       </c>
       <c r="AI2">
-        <v>0.6151515141334689</v>
+        <v>0.6027763306821233</v>
       </c>
       <c r="AJ2">
-        <v>0.5220292772750187</v>
+        <v>0.5465814759112027</v>
       </c>
       <c r="AK2">
-        <v>0.5843200365772676</v>
+        <v>0.5659567747048906</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-2.05</v>
+        <v>-1.17</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Danasupra Erapacific Tbk (IDX:DEFI)</t>
+          <t>PT Pool Advista Finance Tbk (IDX:POLA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,26 +712,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.284</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>-0.261</v>
-      </c>
-      <c r="L3">
-        <v>-2.509615384615385</v>
+        <v>-2.12</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,55 +737,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.444</v>
+        <v>2.56</v>
       </c>
       <c r="V3">
-        <v>0.00923076923076923</v>
+        <v>0.1368983957219251</v>
       </c>
       <c r="W3">
-        <v>-0.0391304347826087</v>
+        <v>-0.1034146341463415</v>
       </c>
       <c r="X3">
-        <v>0.0266280430364044</v>
+        <v>0.05332251242949469</v>
       </c>
       <c r="Y3">
-        <v>-0.06575847781901309</v>
+        <v>-0.1567371465758362</v>
       </c>
       <c r="Z3">
-        <v>0.01665065642010887</v>
+        <v>0</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0266280430364044</v>
+        <v>0.05332339258340158</v>
       </c>
       <c r="AC3">
-        <v>-0.0266280430364044</v>
+        <v>-0.05332339258340158</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG3">
-        <v>-0.444</v>
+        <v>-2.559</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>5.347307630607989e-05</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>5.847611250804046e-05</v>
       </c>
       <c r="AJ3">
-        <v>-0.009316770186335404</v>
+        <v>-0.1585403630506165</v>
       </c>
       <c r="AK3">
-        <v>-0.06700875339571385</v>
+        <v>-0.1759851454507943</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -841,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.444</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L4">
-        <v>0.448938321536906</v>
+        <v>0.9019292604501609</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -868,55 +850,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.7</v>
+        <v>5.74</v>
       </c>
       <c r="V4">
-        <v>0.04787234042553192</v>
+        <v>0.1386473429951691</v>
       </c>
       <c r="W4">
-        <v>0.04601036269430052</v>
+        <v>0.0539423076923077</v>
       </c>
       <c r="X4">
-        <v>0.02662950448157657</v>
+        <v>0.05332483388502991</v>
       </c>
       <c r="Y4">
-        <v>0.01938085821272395</v>
+        <v>0.0006174738072777866</v>
       </c>
       <c r="Z4">
-        <v>0.1699312714776632</v>
+        <v>0.08066398651277397</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.02662990907671087</v>
+        <v>0.05332880815133206</v>
       </c>
       <c r="AC4">
-        <v>-0.02662990907671087</v>
+        <v>-0.05332880815133206</v>
       </c>
       <c r="AD4">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="AG4">
-        <v>-2.689</v>
+        <v>-5.73</v>
       </c>
       <c r="AH4">
-        <v>0.0001949974295793374</v>
+        <v>0.0002414875633904854</v>
       </c>
       <c r="AI4">
-        <v>0.001056574776678513</v>
+        <v>0.0009699321047526673</v>
       </c>
       <c r="AJ4">
-        <v>-0.05006423265252928</v>
+        <v>-0.1606391925988225</v>
       </c>
       <c r="AK4">
-        <v>-0.3487226040721048</v>
+        <v>-1.25382932166302</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -933,7 +915,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Pool Advista Finance Tbk (IDX:POLA)</t>
+          <t>PT Trust Finance Indonesia Tbk (IDX:TRUS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -941,23 +923,29 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.07400000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.142</v>
+      </c>
       <c r="G5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>-2.42</v>
+        <v>1.52</v>
       </c>
       <c r="L5">
-        <v>1.581699346405229</v>
+        <v>0.475</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -966,7 +954,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -975,61 +963,61 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>4.68</v>
+        <v>4.83</v>
       </c>
       <c r="V5">
-        <v>0.1289256198347107</v>
+        <v>0.2698324022346369</v>
       </c>
       <c r="W5">
-        <v>-0.11</v>
+        <v>0.06785714285714287</v>
       </c>
       <c r="X5">
-        <v>0.02663010728653489</v>
+        <v>0.05365768032174052</v>
       </c>
       <c r="Y5">
-        <v>-0.1366301072865349</v>
+        <v>0.01419946253540234</v>
       </c>
       <c r="Z5">
-        <v>-0.07088584136397331</v>
+        <v>0.1749303012081124</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.02663222921616524</v>
+        <v>0.0540847579029699</v>
       </c>
       <c r="AC5">
-        <v>-0.02663222921616524</v>
+        <v>-0.0540847579029699</v>
       </c>
       <c r="AD5">
-        <v>0.01</v>
+        <v>0.487</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.01</v>
+        <v>0.487</v>
       </c>
       <c r="AG5">
-        <v>-4.67</v>
+        <v>-4.343</v>
       </c>
       <c r="AH5">
-        <v>0.0002754062241806665</v>
+        <v>0.02648610431282972</v>
       </c>
       <c r="AI5">
-        <v>0.0004875670404680643</v>
+        <v>0.02109412223329146</v>
       </c>
       <c r="AJ5">
-        <v>-0.1476446411634524</v>
+        <v>-0.3203511101276094</v>
       </c>
       <c r="AK5">
-        <v>-0.2950094756790903</v>
+        <v>-0.2378813605740264</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1046,7 +1034,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Trust Finance Indonesia Tbk (IDX:TRUS)</t>
+          <t>PT Woori Finance Indonesia Tbk (IDX:BPFI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1055,10 +1043,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.08109999999999999</v>
+        <v>0.0199</v>
       </c>
       <c r="E6">
-        <v>0.168</v>
+        <v>0.16</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1073,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1.85</v>
+        <v>4.71</v>
       </c>
       <c r="L6">
-        <v>0.5538922155688624</v>
+        <v>0.3270833333333333</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1100,55 +1088,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>4.49</v>
+        <v>5.36</v>
       </c>
       <c r="V6">
-        <v>0.1927038626609442</v>
+        <v>0.04710017574692443</v>
       </c>
       <c r="W6">
-        <v>0.09343434343434344</v>
+        <v>0.07476190476190477</v>
       </c>
       <c r="X6">
-        <v>0.02675121498120752</v>
+        <v>0.05542611724137759</v>
       </c>
       <c r="Y6">
-        <v>0.06668312845313591</v>
+        <v>0.01933578752052718</v>
       </c>
       <c r="Z6">
-        <v>0.1931529030765672</v>
+        <v>0.1735776277724204</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.02681482783411782</v>
+        <v>0.05751702847242857</v>
       </c>
       <c r="AC6">
-        <v>-0.02681482783411782</v>
+        <v>-0.05751702847242857</v>
       </c>
       <c r="AD6">
-        <v>0.383</v>
+        <v>19.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.383</v>
+        <v>19.4</v>
       </c>
       <c r="AG6">
-        <v>-4.107</v>
+        <v>14.04</v>
       </c>
       <c r="AH6">
-        <v>0.01617193767681459</v>
+        <v>0.1456456456456456</v>
       </c>
       <c r="AI6">
-        <v>0.01681077996751964</v>
+        <v>0.2345828295042322</v>
       </c>
       <c r="AJ6">
-        <v>-0.2139842650966498</v>
+        <v>0.1098247809762203</v>
       </c>
       <c r="AK6">
-        <v>-0.2245121084567868</v>
+        <v>0.1815360744763382</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1165,7 +1153,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT Batavia Prosperindo Finance Tbk (IDX:BPFI)</t>
+          <t>PT Mandala Multifinance Tbk (IDX:MFIN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1174,10 +1162,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0774</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E7">
-        <v>0.0864</v>
+        <v>0.192</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1192,82 +1180,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>2.91</v>
+        <v>45.5</v>
       </c>
       <c r="L7">
-        <v>0.1927152317880795</v>
+        <v>0.4366602687140115</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>12.7</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.04524403277520484</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.2791208791208791</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>12.7</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.04524403277520484</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.2791208791208791</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>5.24</v>
+        <v>85.2</v>
       </c>
       <c r="V7">
-        <v>0.02915971062882582</v>
+        <v>0.3035268970431065</v>
       </c>
       <c r="W7">
-        <v>0.05132275132275133</v>
+        <v>0.2497255762897914</v>
       </c>
       <c r="X7">
-        <v>0.02767884629147565</v>
+        <v>0.06210790928794706</v>
       </c>
       <c r="Y7">
-        <v>0.02364390503127568</v>
+        <v>0.1876176670018444</v>
       </c>
       <c r="Z7">
-        <v>0.1613247863247863</v>
+        <v>0.3697657913413769</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.02743581785571304</v>
+        <v>0.06123442832765591</v>
       </c>
       <c r="AC7">
-        <v>-0.02743581785571304</v>
+        <v>-0.06123442832765591</v>
       </c>
       <c r="AD7">
-        <v>25.2</v>
+        <v>199.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>25.2</v>
+        <v>199.8</v>
       </c>
       <c r="AG7">
-        <v>19.96</v>
+        <v>114.6</v>
       </c>
       <c r="AH7">
-        <v>0.12298682284041</v>
+        <v>0.4158168574401665</v>
       </c>
       <c r="AI7">
-        <v>0.2857142857142857</v>
+        <v>0.4956586454973952</v>
       </c>
       <c r="AJ7">
-        <v>0.09996994891315236</v>
+        <v>0.289906400202378</v>
       </c>
       <c r="AK7">
-        <v>0.2405978784956606</v>
+        <v>0.3604907203523121</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1284,7 +1275,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT Radana Bhaskara Finance Tbk (IDX:HDFA)</t>
+          <t>PT BFI Finance Indonesia Tbk (IDX:BFIN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1293,7 +1284,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.261</v>
+        <v>0.0803</v>
+      </c>
+      <c r="E8">
+        <v>0.0864</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1308,82 +1302,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>-1.73</v>
+        <v>108</v>
       </c>
       <c r="L8">
-        <v>-0.2559171597633136</v>
+        <v>0.4395604395604396</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>16.7</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.01652810768012668</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>0.1546296296296296</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>16.7</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.01652810768012668</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>0.1546296296296296</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>3.11</v>
+        <v>86.7</v>
       </c>
       <c r="V8">
-        <v>0.03297985153764581</v>
+        <v>0.08580760095011877</v>
       </c>
       <c r="W8">
-        <v>-0.04752747252747253</v>
+        <v>0.214583747268031</v>
       </c>
       <c r="X8">
-        <v>0.02888475220344602</v>
+        <v>0.06157655670521376</v>
       </c>
       <c r="Y8">
-        <v>-0.07641222473091855</v>
+        <v>0.1530071905628172</v>
       </c>
       <c r="Z8">
-        <v>0.1867403314917127</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.02884300315515288</v>
+        <v>0.06357056056454763</v>
       </c>
       <c r="AC8">
-        <v>-0.02884300315515288</v>
+        <v>-0.06357056056454763</v>
       </c>
       <c r="AD8">
-        <v>28.4</v>
+        <v>675.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>28.4</v>
+        <v>675.7</v>
       </c>
       <c r="AG8">
-        <v>25.29</v>
+        <v>589</v>
       </c>
       <c r="AH8">
-        <v>0.2314588427057865</v>
+        <v>0.4007472866378033</v>
       </c>
       <c r="AI8">
-        <v>0.4329268292682927</v>
+        <v>0.5448314787937429</v>
       </c>
       <c r="AJ8">
-        <v>0.2114725311480893</v>
+        <v>0.3682630986619982</v>
       </c>
       <c r="AK8">
-        <v>0.4047047527604417</v>
+        <v>0.5106198526224534</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1400,7 +1397,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT BFI Finance Indonesia Tbk (IDX:BFIN)</t>
+          <t>PT Adira Dinamika Multi Finance Tbk (IDX:ADMF)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1409,10 +1406,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0645</v>
+        <v>0.0521</v>
       </c>
       <c r="E9">
-        <v>0.0546</v>
+        <v>0.0604</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1427,28 +1424,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>68.40000000000001</v>
+        <v>105.4</v>
       </c>
       <c r="L9">
-        <v>0.3741794310722101</v>
+        <v>0.312759643916914</v>
       </c>
       <c r="M9">
-        <v>18.9</v>
+        <v>39.9</v>
       </c>
       <c r="N9">
-        <v>0.01535586610334741</v>
+        <v>0.06927083333333334</v>
       </c>
       <c r="O9">
-        <v>0.2763157894736842</v>
+        <v>0.3785578747628083</v>
       </c>
       <c r="P9">
-        <v>18.9</v>
+        <v>39.9</v>
       </c>
       <c r="Q9">
-        <v>0.01535586610334741</v>
+        <v>0.06927083333333334</v>
       </c>
       <c r="R9">
-        <v>0.2763157894736842</v>
+        <v>0.3785578747628083</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1457,55 +1454,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>57.8</v>
+        <v>149.3</v>
       </c>
       <c r="V9">
-        <v>0.04696132596685083</v>
+        <v>0.2592013888888889</v>
       </c>
       <c r="W9">
-        <v>0.1614730878186969</v>
+        <v>0.1815363417154668</v>
       </c>
       <c r="X9">
-        <v>0.02947179245669845</v>
+        <v>0.06876417835227283</v>
       </c>
       <c r="Y9">
-        <v>0.1320012953619984</v>
+        <v>0.1127721633631939</v>
       </c>
       <c r="Z9">
-        <v>0.1959061193869896</v>
+        <v>0.2534978185647661</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.02926067344042983</v>
+        <v>0.06389742862538933</v>
       </c>
       <c r="AC9">
-        <v>-0.02926067344042983</v>
+        <v>-0.06389742862538933</v>
       </c>
       <c r="AD9">
-        <v>467.1</v>
+        <v>720.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>467.1</v>
+        <v>720.6</v>
       </c>
       <c r="AG9">
-        <v>409.3</v>
+        <v>571.3</v>
       </c>
       <c r="AH9">
-        <v>0.275104540903469</v>
+        <v>0.5557612216566405</v>
       </c>
       <c r="AI9">
-        <v>0.4813478977741137</v>
+        <v>0.5365199910654457</v>
       </c>
       <c r="AJ9">
-        <v>0.2495579537833059</v>
+        <v>0.4979517127168134</v>
       </c>
       <c r="AK9">
-        <v>0.4484987946526408</v>
+        <v>0.478555872005361</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1522,7 +1519,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pt Mandala Multifinance Tbk (IDX:MFIN)</t>
+          <t>PT Radana Bhaskara Finance Tbk (IDX:HDFA)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1531,10 +1528,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.00645</v>
-      </c>
-      <c r="E10">
-        <v>0.03759999999999999</v>
+        <v>-0.0003500000000000001</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1549,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>22.1</v>
+        <v>2.51</v>
       </c>
       <c r="L10">
-        <v>0.2735148514851485</v>
+        <v>0.3653566229985444</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1576,55 +1570,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>42.9</v>
+        <v>3.65</v>
       </c>
       <c r="V10">
-        <v>0.2121661721068249</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="W10">
-        <v>0.1414852752880922</v>
+        <v>0.06747311827956988</v>
       </c>
       <c r="X10">
-        <v>0.03190887877451992</v>
+        <v>0.06344846825396978</v>
       </c>
       <c r="Y10">
-        <v>0.1095763965135723</v>
+        <v>0.004024650025600096</v>
       </c>
       <c r="Z10">
-        <v>0.3264646464646465</v>
+        <v>0.1099375900144023</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.02934326482091893</v>
+        <v>0.06484725545067302</v>
       </c>
       <c r="AC10">
-        <v>-0.02934326482091893</v>
+        <v>-0.06484725545067302</v>
       </c>
       <c r="AD10">
-        <v>142.5</v>
+        <v>53.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>142.5</v>
+        <v>53.9</v>
       </c>
       <c r="AG10">
-        <v>99.59999999999999</v>
+        <v>50.25</v>
       </c>
       <c r="AH10">
-        <v>0.4134029590948651</v>
+        <v>0.4506688963210703</v>
       </c>
       <c r="AI10">
-        <v>0.4388666461348938</v>
+        <v>0.5556701030927835</v>
       </c>
       <c r="AJ10">
-        <v>0.3300198807157058</v>
+        <v>0.4333764553686934</v>
       </c>
       <c r="AK10">
-        <v>0.3534421575585522</v>
+        <v>0.5382967327262989</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1641,7 +1635,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PT Adira Dinamika Multi Finance Tbk (IDX:ADMF)</t>
+          <t>PT KDB Tifa Finance Tbk (IDX:TIFA)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1650,10 +1644,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0158</v>
+        <v>0.103</v>
       </c>
       <c r="E11">
-        <v>-0.0338</v>
+        <v>0.203</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1668,85 +1662,82 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>67.5</v>
+        <v>3.84</v>
       </c>
       <c r="L11">
-        <v>0.235519888346127</v>
+        <v>0.4665856622114216</v>
       </c>
       <c r="M11">
-        <v>35.9</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.06660482374768088</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.5318518518518518</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>35.9</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.06660482374768088</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.5318518518518518</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>108.8</v>
+        <v>16.3</v>
       </c>
       <c r="V11">
-        <v>0.2018552875695733</v>
+        <v>0.1765980498374865</v>
       </c>
       <c r="W11">
-        <v>0.1309916553464002</v>
+        <v>0.05363128491620112</v>
       </c>
       <c r="X11">
-        <v>0.0385504777492305</v>
+        <v>0.05669192902174643</v>
       </c>
       <c r="Y11">
-        <v>0.09244117759716966</v>
+        <v>-0.00306064410554531</v>
       </c>
       <c r="Z11">
-        <v>0.1908630793819926</v>
+        <v>0.1402044293015332</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.03066119385916526</v>
+        <v>0.06928878526715473</v>
       </c>
       <c r="AC11">
-        <v>-0.03066119385916526</v>
+        <v>-0.06928878526715473</v>
       </c>
       <c r="AD11">
-        <v>857.6</v>
+        <v>25.2</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>857.6</v>
+        <v>25.2</v>
       </c>
       <c r="AG11">
-        <v>748.8000000000001</v>
+        <v>8.899999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.6140627237576973</v>
+        <v>0.214468085106383</v>
       </c>
       <c r="AI11">
-        <v>0.5963009317202058</v>
+        <v>0.2619542619542619</v>
       </c>
       <c r="AJ11">
-        <v>0.581456747942227</v>
+        <v>0.08794466403162055</v>
       </c>
       <c r="AK11">
-        <v>0.5632616217842636</v>
+        <v>0.1113892365456821</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1772,10 +1763,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.1</v>
+        <v>-0.16</v>
       </c>
       <c r="E12">
-        <v>-0.191</v>
+        <v>-0.271</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1790,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>4.16</v>
+        <v>3.13</v>
       </c>
       <c r="L12">
-        <v>0.05977011494252874</v>
+        <v>0.1298755186721992</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1817,55 +1808,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>37.1</v>
+        <v>3.14</v>
       </c>
       <c r="V12">
-        <v>0.5322812051649928</v>
+        <v>0.04104575163398693</v>
       </c>
       <c r="W12">
-        <v>0.01300813008130081</v>
+        <v>0.009276822762299941</v>
       </c>
       <c r="X12">
-        <v>0.04688233500538693</v>
+        <v>0.07455602755242061</v>
       </c>
       <c r="Y12">
-        <v>-0.03387420492408612</v>
+        <v>-0.06527920479012067</v>
       </c>
       <c r="Z12">
-        <v>0.1090738128819934</v>
+        <v>0.0493145078780438</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.03142233659091176</v>
+        <v>0.0694945455275057</v>
       </c>
       <c r="AC12">
-        <v>-0.03142233659091176</v>
+        <v>-0.0694945455275057</v>
       </c>
       <c r="AD12">
-        <v>188.4</v>
+        <v>131.6</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>188.4</v>
+        <v>131.6</v>
       </c>
       <c r="AG12">
-        <v>151.3</v>
+        <v>128.46</v>
       </c>
       <c r="AH12">
-        <v>0.7299496319256101</v>
+        <v>0.632388274867852</v>
       </c>
       <c r="AI12">
-        <v>0.3583111449220236</v>
+        <v>0.2910216718266254</v>
       </c>
       <c r="AJ12">
-        <v>0.6846153846153846</v>
+        <v>0.6267564402810305</v>
       </c>
       <c r="AK12">
-        <v>0.309596889707387</v>
+        <v>0.2860642230436912</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1891,10 +1882,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.00638</v>
+        <v>0.0189</v>
       </c>
       <c r="E13">
-        <v>-0.0237</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1909,82 +1900,85 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>5.37</v>
+        <v>10.4</v>
       </c>
       <c r="L13">
-        <v>0.09388111888111887</v>
+        <v>0.1533923303834808</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>2.16</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.03756521739130435</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>0.2076923076923077</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>2.16</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.03756521739130435</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.2076923076923077</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>23.6</v>
+        <v>41.2</v>
       </c>
       <c r="V13">
-        <v>0.3933333333333334</v>
+        <v>0.7165217391304348</v>
       </c>
       <c r="W13">
-        <v>0.07336065573770492</v>
+        <v>0.1152993348115299</v>
       </c>
       <c r="X13">
-        <v>0.05451533981171967</v>
+        <v>0.1068822321040607</v>
       </c>
       <c r="Y13">
-        <v>0.01884531592598525</v>
+        <v>0.008417102707469273</v>
       </c>
       <c r="Z13">
-        <v>0.1360608943862988</v>
+        <v>0.2256990679094541</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.03180499192175879</v>
+        <v>0.07410592791926007</v>
       </c>
       <c r="AC13">
-        <v>-0.03180499192175879</v>
+        <v>-0.07410592791926007</v>
       </c>
       <c r="AD13">
-        <v>223.3</v>
+        <v>249.5</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>223.3</v>
+        <v>249.5</v>
       </c>
       <c r="AG13">
-        <v>199.7</v>
+        <v>208.3</v>
       </c>
       <c r="AH13">
-        <v>0.7882103776914932</v>
+        <v>0.8127035830618893</v>
       </c>
       <c r="AI13">
-        <v>0.7242945183263055</v>
+        <v>0.7265579499126383</v>
       </c>
       <c r="AJ13">
-        <v>0.7689641894493646</v>
+        <v>0.7836719337848006</v>
       </c>
       <c r="AK13">
-        <v>0.7014401123990165</v>
+        <v>0.6892786234281932</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2001,7 +1995,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PT KDB Tifa Finance Tbk (IDX:TIFA)</t>
+          <t>PT Mizuho Leasing Indonesia Tbk (IDX:VRNA)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2010,10 +2004,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.028</v>
+        <v>0.218</v>
       </c>
       <c r="E14">
-        <v>-0.0738</v>
+        <v>0.352</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2028,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0.797</v>
+        <v>2.2</v>
       </c>
       <c r="L14">
-        <v>0.1454379562043795</v>
+        <v>0.1189189189189189</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2055,55 +2049,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>37.6</v>
+        <v>4.31</v>
       </c>
       <c r="V14">
-        <v>0.8086021505376344</v>
+        <v>0.1149333333333333</v>
       </c>
       <c r="W14">
-        <v>0.0303041825095057</v>
+        <v>0.04782608695652174</v>
       </c>
       <c r="X14">
-        <v>0.03060831682026402</v>
+        <v>0.08900301168118203</v>
       </c>
       <c r="Y14">
-        <v>-0.0003041343107583194</v>
+        <v>-0.04117692472466029</v>
       </c>
       <c r="Z14">
-        <v>0.09658089531194926</v>
+        <v>0.1199429460580913</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.03190108323551409</v>
+        <v>0.07472248852405076</v>
       </c>
       <c r="AC14">
-        <v>-0.03190108323551409</v>
+        <v>-0.07472248852405076</v>
       </c>
       <c r="AD14">
-        <v>24.7</v>
+        <v>108.4</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>24.7</v>
+        <v>108.4</v>
       </c>
       <c r="AG14">
-        <v>-12.9</v>
+        <v>104.09</v>
       </c>
       <c r="AH14">
-        <v>0.3469101123595505</v>
+        <v>0.7429746401644962</v>
       </c>
       <c r="AI14">
-        <v>0.2564901349948079</v>
+        <v>0.7066492829204694</v>
       </c>
       <c r="AJ14">
-        <v>-0.3839285714285716</v>
+        <v>0.7351507874849919</v>
       </c>
       <c r="AK14">
-        <v>-0.2197614991482113</v>
+        <v>0.6981688912737273</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2120,7 +2114,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PT. Verena Multi Finance Tbk (IDX:VRNA)</t>
+          <t>PT Buana Finance Tbk (IDX:BBLD)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2129,10 +2123,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.163</v>
+        <v>-0.00843</v>
       </c>
       <c r="E15">
-        <v>0.41</v>
+        <v>-0.00235</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2147,82 +2141,85 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>1.81</v>
+        <v>4.45</v>
       </c>
       <c r="L15">
-        <v>0.1190789473684211</v>
+        <v>0.2170731707317073</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>0.648</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.01007776049766719</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.1456179775280899</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>0.648</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.01007776049766719</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.1456179775280899</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>2.36</v>
+        <v>25.4</v>
       </c>
       <c r="V15">
-        <v>0.03953098827470686</v>
+        <v>0.3950233281493001</v>
       </c>
       <c r="W15">
-        <v>0.04268867924528302</v>
+        <v>0.05186480186480187</v>
       </c>
       <c r="X15">
-        <v>0.0405099695671768</v>
+        <v>0.08902799318186769</v>
       </c>
       <c r="Y15">
-        <v>0.002178709678106225</v>
+        <v>-0.03716319131706582</v>
       </c>
       <c r="Z15">
-        <v>0.09251369446135117</v>
+        <v>0.09018917729872415</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03284292110714337</v>
+        <v>0.07472633759905567</v>
       </c>
       <c r="AC15">
-        <v>-0.03284292110714337</v>
+        <v>-0.07472633759905567</v>
       </c>
       <c r="AD15">
-        <v>110.6</v>
+        <v>186</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>110.6</v>
+        <v>186</v>
       </c>
       <c r="AG15">
-        <v>108.24</v>
+        <v>160.6</v>
       </c>
       <c r="AH15">
-        <v>0.6494421608925425</v>
+        <v>0.7431082700759088</v>
       </c>
       <c r="AI15">
-        <v>0.7062579821200511</v>
+        <v>0.6881243063263041</v>
       </c>
       <c r="AJ15">
-        <v>0.6445158985351911</v>
+        <v>0.7140951534015119</v>
       </c>
       <c r="AK15">
-        <v>0.7017634854771784</v>
+        <v>0.6557778685177624</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2239,7 +2236,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PT Buana Finance Tbk (IDX:BBLD)</t>
+          <t>PT Indomobil Multi Jasa Tbk (IDX:IMJS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2248,10 +2245,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.039</v>
+        <v>0.106</v>
       </c>
       <c r="E16">
-        <v>-0.214</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2266,28 +2263,28 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>1.17</v>
+        <v>6.64</v>
       </c>
       <c r="L16">
-        <v>0.05879396984924623</v>
+        <v>0.02346289752650177</v>
       </c>
       <c r="M16">
-        <v>0.46</v>
+        <v>0.142</v>
       </c>
       <c r="N16">
-        <v>0.0107981220657277</v>
+        <v>0.0008114285714285713</v>
       </c>
       <c r="O16">
-        <v>0.3931623931623932</v>
+        <v>0.0213855421686747</v>
       </c>
       <c r="P16">
-        <v>0.46</v>
+        <v>0.142</v>
       </c>
       <c r="Q16">
-        <v>0.0107981220657277</v>
+        <v>0.0008114285714285713</v>
       </c>
       <c r="R16">
-        <v>0.3931623931623932</v>
+        <v>0.0213855421686747</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2296,299 +2293,64 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>19</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="V16">
-        <v>0.4460093896713615</v>
+        <v>0.4862857142857143</v>
       </c>
       <c r="W16">
-        <v>0.01451612903225807</v>
+        <v>0.02665596146126054</v>
       </c>
       <c r="X16">
-        <v>0.05485957096534545</v>
+        <v>0.1461314255941585</v>
       </c>
       <c r="Y16">
-        <v>-0.04034344193308739</v>
+        <v>-0.1194754641328979</v>
       </c>
       <c r="Z16">
-        <v>0.07896825396825397</v>
+        <v>0.1860006572461387</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.03419040128193587</v>
+        <v>0.07589380010060834</v>
       </c>
       <c r="AC16">
-        <v>-0.03419040128193587</v>
+        <v>-0.07589380010060834</v>
       </c>
       <c r="AD16">
-        <v>160.5</v>
+        <v>1315.8</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>160.5</v>
+        <v>1315.8</v>
       </c>
       <c r="AG16">
-        <v>141.5</v>
+        <v>1230.7</v>
       </c>
       <c r="AH16">
-        <v>0.7902511078286558</v>
+        <v>0.8826133619533136</v>
       </c>
       <c r="AI16">
-        <v>0.6516443361753959</v>
+        <v>0.8308916393028543</v>
       </c>
       <c r="AJ16">
-        <v>0.7686040195545899</v>
+        <v>0.8755068649071637</v>
       </c>
       <c r="AK16">
-        <v>0.6225252969643642</v>
+        <v>0.821287954621288</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PT Indomobil Multi Jasa Tbk (IDX:IMJS)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>0.105</v>
-      </c>
-      <c r="E17">
-        <v>-0.507</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0.214</v>
-      </c>
-      <c r="L17">
-        <v>0.000837245696400626</v>
-      </c>
-      <c r="M17">
-        <v>0.01</v>
-      </c>
-      <c r="N17">
-        <v>3.930817610062893e-05</v>
-      </c>
-      <c r="O17">
-        <v>0.04672897196261683</v>
-      </c>
-      <c r="P17">
-        <v>0.01</v>
-      </c>
-      <c r="Q17">
-        <v>3.930817610062893e-05</v>
-      </c>
-      <c r="R17">
-        <v>0.04672897196261683</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>90.5</v>
-      </c>
-      <c r="V17">
-        <v>0.3557389937106918</v>
-      </c>
-      <c r="W17">
-        <v>0.0009511111111111111</v>
-      </c>
-      <c r="X17">
-        <v>0.06677159808870435</v>
-      </c>
-      <c r="Y17">
-        <v>-0.06582048697759324</v>
-      </c>
-      <c r="Z17">
-        <v>0.1723533378287256</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0.03469232192485894</v>
-      </c>
-      <c r="AC17">
-        <v>-0.03469232192485894</v>
-      </c>
-      <c r="AD17">
-        <v>1362.9</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>1362.9</v>
-      </c>
-      <c r="AG17">
-        <v>1272.4</v>
-      </c>
-      <c r="AH17">
-        <v>0.8427007976256724</v>
-      </c>
-      <c r="AI17">
-        <v>0.8364428624033386</v>
-      </c>
-      <c r="AJ17">
-        <v>0.8333769976421272</v>
-      </c>
-      <c r="AK17">
-        <v>0.8268243550588082</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>-2.05</v>
-      </c>
-      <c r="AQ17">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PT Intan Baruprana Finance Tbk (IDX:IBFN)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G18">
-        <v>-0</v>
-      </c>
-      <c r="H18">
-        <v>-0</v>
-      </c>
-      <c r="I18">
-        <v>-0</v>
-      </c>
-      <c r="J18">
-        <v>-0</v>
-      </c>
-      <c r="K18">
-        <v>-43.7</v>
-      </c>
-      <c r="L18">
-        <v>1.203856749311295</v>
-      </c>
-      <c r="M18">
-        <v>-0</v>
-      </c>
-      <c r="N18">
-        <v>-0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>-0</v>
-      </c>
-      <c r="Q18">
-        <v>-0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>1.23</v>
-      </c>
-      <c r="V18">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="W18">
-        <v>-2.894039735099338</v>
-      </c>
-      <c r="X18">
-        <v>0.1186615921902775</v>
-      </c>
-      <c r="Y18">
-        <v>-3.012701327289616</v>
-      </c>
-      <c r="Z18">
-        <v>-0.4331277070481691</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>0.03547712796059482</v>
-      </c>
-      <c r="AC18">
-        <v>-0.03547712796059482</v>
-      </c>
-      <c r="AD18">
-        <v>70.5</v>
-      </c>
-      <c r="AE18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>70.5</v>
-      </c>
-      <c r="AG18">
-        <v>69.27</v>
-      </c>
-      <c r="AH18">
-        <v>0.9247114375655824</v>
-      </c>
-      <c r="AI18">
-        <v>1.654929577464789</v>
-      </c>
-      <c r="AJ18">
-        <v>0.9234768697507</v>
-      </c>
-      <c r="AK18">
-        <v>1.674401740391588</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
+        <v>-1.17</v>
+      </c>
+      <c r="AQ16">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/indonesia/indonesia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ16"/>
+  <dimension ref="A1:AQ21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06080000000000001</v>
+        <v>0.0547</v>
       </c>
       <c r="E2">
-        <v>0.0864</v>
+        <v>0.05695</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.009504302325790406</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.009504302325790406</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.01047675198219752</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.008246936023567445</v>
       </c>
       <c r="K2">
-        <v>296.741</v>
+        <v>369.812</v>
       </c>
       <c r="L2">
-        <v>0.2616482177402431</v>
+        <v>0.1661846360144304</v>
       </c>
       <c r="M2">
-        <v>72.25</v>
+        <v>162.28</v>
       </c>
       <c r="N2">
-        <v>0.02749552840887468</v>
+        <v>0.04366732323721571</v>
       </c>
       <c r="O2">
-        <v>0.2434783194772546</v>
+        <v>0.4388175613554995</v>
       </c>
       <c r="P2">
-        <v>72.25</v>
+        <v>162.28</v>
       </c>
       <c r="Q2">
-        <v>0.02749552840887468</v>
+        <v>0.04366732323721571</v>
       </c>
       <c r="R2">
-        <v>0.2434783194772546</v>
+        <v>0.4388175613554995</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,64 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>518.79</v>
+        <v>581.4</v>
       </c>
       <c r="V2">
-        <v>0.1974312136088595</v>
+        <v>0.1564467693499952</v>
       </c>
       <c r="W2">
-        <v>0.06070771298593879</v>
+        <v>0.07097378277153558</v>
       </c>
       <c r="X2">
-        <v>0.06277818877095842</v>
+        <v>0.06398150662671885</v>
       </c>
       <c r="Y2">
-        <v>-0.002070475785019635</v>
+        <v>0.006992276144816734</v>
       </c>
       <c r="Z2">
-        <v>0.2076414831110796</v>
+        <v>0.3894860668174571</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06437234203803117</v>
+        <v>0.06185060978166303</v>
       </c>
       <c r="AC2">
-        <v>-0.06437234203803117</v>
+        <v>-0.06213770537916003</v>
       </c>
       <c r="AD2">
-        <v>3686.398</v>
+        <v>4780.65</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3686.398</v>
+        <v>4780.65</v>
       </c>
       <c r="AG2">
-        <v>3167.608</v>
+        <v>4199.25</v>
       </c>
       <c r="AH2">
-        <v>0.5838360443566128</v>
+        <v>0.5626326214291514</v>
       </c>
       <c r="AI2">
-        <v>0.6027763306821233</v>
+        <v>0.6334545743644784</v>
       </c>
       <c r="AJ2">
-        <v>0.5465814759112027</v>
+        <v>0.5305077486914963</v>
       </c>
       <c r="AK2">
-        <v>0.5659567747048906</v>
+        <v>0.6028597885306974</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.909</v>
       </c>
       <c r="AM2">
-        <v>-1.17</v>
+        <v>-0.9249999999999998</v>
+      </c>
+      <c r="AN2">
+        <v>161.2197754021515</v>
+      </c>
+      <c r="AO2">
+        <v>12.21267679413305</v>
+      </c>
+      <c r="AP2">
+        <v>141.6129902539372</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>-25.20432432432433</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PT Pool Advista Finance Tbk (IDX:POLA)</t>
+          <t>PT Jasuindo Tiga Perkasa Tbk (IDX:JTPE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,86 +721,122 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.133</v>
+      </c>
+      <c r="E3">
+        <v>0.213</v>
+      </c>
+      <c r="G3">
+        <v>0.1044148563419762</v>
+      </c>
+      <c r="H3">
+        <v>0.1044148563419762</v>
+      </c>
+      <c r="I3">
+        <v>0.1492641906096707</v>
+      </c>
+      <c r="J3">
+        <v>0.1173525360655342</v>
+      </c>
       <c r="K3">
-        <v>-2.12</v>
+        <v>14.3</v>
+      </c>
+      <c r="L3">
+        <v>0.1002102312543798</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>3.47</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02529154518950438</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.2426573426573427</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3.47</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02529154518950438</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.2426573426573427</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>2.56</v>
+        <v>9.44</v>
       </c>
       <c r="V3">
-        <v>0.1368983957219251</v>
+        <v>0.06880466472303207</v>
       </c>
       <c r="W3">
-        <v>-0.1034146341463415</v>
+        <v>0.2504378283712785</v>
       </c>
       <c r="X3">
-        <v>0.05332251242949469</v>
+        <v>0.05721949666336409</v>
       </c>
       <c r="Y3">
-        <v>-0.1567371465758362</v>
+        <v>0.1932183317079144</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.177960927960927</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.255589238347859</v>
       </c>
       <c r="AB3">
-        <v>0.05332339258340158</v>
+        <v>0.05725526545432437</v>
       </c>
       <c r="AC3">
-        <v>-0.05332339258340158</v>
+        <v>0.1983339728935347</v>
       </c>
       <c r="AD3">
-        <v>0.001</v>
+        <v>7.29</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.001</v>
+        <v>7.29</v>
       </c>
       <c r="AG3">
-        <v>-2.559</v>
+        <v>-2.149999999999999</v>
       </c>
       <c r="AH3">
-        <v>5.347307630607989e-05</v>
+        <v>0.05045331856875909</v>
       </c>
       <c r="AI3">
-        <v>5.847611250804046e-05</v>
+        <v>0.09057025717480431</v>
       </c>
       <c r="AJ3">
-        <v>-0.1585403630506165</v>
+        <v>-0.01592002961865975</v>
       </c>
       <c r="AK3">
-        <v>-0.1759851454507943</v>
+        <v>-0.03026038001407459</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.702</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.5459999999999999</v>
+      </c>
+      <c r="AN3">
+        <v>0.3088983050847458</v>
+      </c>
+      <c r="AO3">
+        <v>30.34188034188034</v>
+      </c>
+      <c r="AP3">
+        <v>-0.0911016949152542</v>
+      </c>
+      <c r="AQ3">
+        <v>39.01098901098901</v>
       </c>
     </row>
     <row r="4">
@@ -802,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PT Fuji Finance Indonesia Tbk (IDX:FUJI)</t>
+          <t>PT M Cash Integrasi Tbk (IDX:MCAS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -810,23 +855,29 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.134</v>
+      </c>
+      <c r="E4">
+        <v>-0.337</v>
+      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.008204681274900398</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.008204681274900398</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.002913346613545816</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.001539349359319479</v>
       </c>
       <c r="K4">
-        <v>0.5610000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="L4">
-        <v>0.9019292604501609</v>
+        <v>0.0006922310756972112</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -850,61 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.74</v>
+        <v>14.2</v>
       </c>
       <c r="V4">
-        <v>0.1386473429951691</v>
+        <v>0.05786471067644661</v>
       </c>
       <c r="W4">
-        <v>0.0539423076923077</v>
+        <v>0.02574074074074074</v>
       </c>
       <c r="X4">
-        <v>0.05332483388502991</v>
+        <v>0.05755459531303002</v>
       </c>
       <c r="Y4">
-        <v>0.0006174738072777866</v>
+        <v>-0.03181385457228927</v>
       </c>
       <c r="Z4">
-        <v>0.08066398651277397</v>
+        <v>41.61442412310242</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.06405913711234677</v>
       </c>
       <c r="AB4">
-        <v>0.05332880815133206</v>
+        <v>0.0574318591634468</v>
       </c>
       <c r="AC4">
-        <v>-0.05332880815133206</v>
+        <v>0.006627277948899973</v>
       </c>
       <c r="AD4">
-        <v>0.01</v>
+        <v>19</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.01</v>
+        <v>19</v>
       </c>
       <c r="AG4">
-        <v>-5.73</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.0002414875633904854</v>
+        <v>0.07186081694402421</v>
       </c>
       <c r="AI4">
-        <v>0.0009699321047526673</v>
+        <v>0.198744769874477</v>
       </c>
       <c r="AJ4">
-        <v>-0.1606391925988225</v>
+        <v>0.01918465227817746</v>
       </c>
       <c r="AK4">
-        <v>-1.25382932166302</v>
+        <v>0.05896805896805898</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="AN4">
+        <v>3.104575163398693</v>
+      </c>
+      <c r="AO4">
+        <v>2.070796460176991</v>
+      </c>
+      <c r="AP4">
+        <v>0.7843137254901962</v>
+      </c>
+      <c r="AQ4">
+        <v>4.148936170212767</v>
       </c>
     </row>
     <row r="5">
@@ -915,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT Trust Finance Indonesia Tbk (IDX:TRUS)</t>
+          <t>PT Pool Advista Finance Tbk (IDX:POLA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -923,12 +986,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.07400000000000001</v>
-      </c>
-      <c r="E5">
-        <v>0.142</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -942,10 +999,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1.52</v>
+        <v>-1.34</v>
       </c>
       <c r="L5">
-        <v>0.475</v>
+        <v>-3.592493297587132</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -954,7 +1011,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -963,61 +1020,61 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>4.83</v>
+        <v>1.45</v>
       </c>
       <c r="V5">
-        <v>0.2698324022346369</v>
+        <v>0.1330275229357798</v>
       </c>
       <c r="W5">
-        <v>0.06785714285714287</v>
+        <v>-0.0783625730994152</v>
       </c>
       <c r="X5">
-        <v>0.05365768032174052</v>
+        <v>0.05648648716400571</v>
       </c>
       <c r="Y5">
-        <v>0.01419946253540234</v>
+        <v>-0.1348490602634209</v>
       </c>
       <c r="Z5">
-        <v>0.1749303012081124</v>
+        <v>0.02565160580427756</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0540847579029699</v>
+        <v>0.05648648716400571</v>
       </c>
       <c r="AC5">
-        <v>-0.0540847579029699</v>
+        <v>-0.05648648716400571</v>
       </c>
       <c r="AD5">
-        <v>0.487</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.487</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-4.343</v>
+        <v>-1.45</v>
       </c>
       <c r="AH5">
-        <v>0.02648610431282972</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.02109412223329146</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.3203511101276094</v>
+        <v>-0.1534391534391534</v>
       </c>
       <c r="AK5">
-        <v>-0.2378813605740264</v>
+        <v>-0.103202846975089</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1034,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PT Woori Finance Indonesia Tbk (IDX:BPFI)</t>
+          <t>PT Fuji Finance Indonesia Tbk (IDX:FUJI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1042,12 +1099,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.0199</v>
-      </c>
-      <c r="E6">
-        <v>0.16</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1061,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>4.71</v>
+        <v>0.21</v>
       </c>
       <c r="L6">
-        <v>0.3270833333333333</v>
+        <v>0.2110552763819095</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1088,55 +1139,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>5.36</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="V6">
-        <v>0.04710017574692443</v>
+        <v>0.3707964601769911</v>
       </c>
       <c r="W6">
-        <v>0.07476190476190477</v>
+        <v>0.0203883495145631</v>
       </c>
       <c r="X6">
-        <v>0.05542611724137759</v>
+        <v>0.05649259134984107</v>
       </c>
       <c r="Y6">
-        <v>0.01933578752052718</v>
+        <v>-0.03610424183527797</v>
       </c>
       <c r="Z6">
-        <v>0.1735776277724204</v>
+        <v>0.2177242888402626</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05751702847242857</v>
+        <v>0.05649322640227131</v>
       </c>
       <c r="AC6">
-        <v>-0.05751702847242857</v>
+        <v>-0.05649322640227131</v>
       </c>
       <c r="AD6">
-        <v>19.4</v>
+        <v>0.01</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>19.4</v>
+        <v>0.01</v>
       </c>
       <c r="AG6">
-        <v>14.04</v>
+        <v>-8.370000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.1456456456456456</v>
+        <v>0.000442282176028306</v>
       </c>
       <c r="AI6">
-        <v>0.2345828295042322</v>
+        <v>0.0009699321047526673</v>
       </c>
       <c r="AJ6">
-        <v>0.1098247809762203</v>
+        <v>-0.5881939564300773</v>
       </c>
       <c r="AK6">
-        <v>0.1815360744763382</v>
+        <v>-4.336787564766841</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1153,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PT Mandala Multifinance Tbk (IDX:MFIN)</t>
+          <t>PT KDB Tifa Finance Tbk (IDX:TIFA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1162,10 +1213,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.06950000000000001</v>
+        <v>0.0526</v>
       </c>
       <c r="E7">
-        <v>0.192</v>
+        <v>0.153</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1180,85 +1231,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>45.5</v>
+        <v>3.44</v>
       </c>
       <c r="L7">
-        <v>0.4366602687140115</v>
+        <v>0.4359949302915083</v>
       </c>
       <c r="M7">
-        <v>12.7</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.04524403277520484</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.2791208791208791</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>12.7</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.04524403277520484</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.2791208791208791</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>85.2</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="V7">
-        <v>0.3035268970431065</v>
+        <v>0.06628914057295136</v>
       </c>
       <c r="W7">
-        <v>0.2497255762897914</v>
+        <v>0.04845070422535211</v>
       </c>
       <c r="X7">
-        <v>0.06210790928794706</v>
+        <v>0.05962975652834293</v>
       </c>
       <c r="Y7">
-        <v>0.1876176670018444</v>
+        <v>-0.01117905230299082</v>
       </c>
       <c r="Z7">
-        <v>0.3697657913413769</v>
+        <v>0.09874843554443052</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06123442832765591</v>
+        <v>0.05808649003961073</v>
       </c>
       <c r="AC7">
-        <v>-0.06123442832765591</v>
+        <v>-0.05808649003961073</v>
       </c>
       <c r="AD7">
-        <v>199.8</v>
+        <v>34.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>199.8</v>
+        <v>34.2</v>
       </c>
       <c r="AG7">
-        <v>114.6</v>
+        <v>24.25</v>
       </c>
       <c r="AH7">
-        <v>0.4158168574401665</v>
+        <v>0.1855670103092784</v>
       </c>
       <c r="AI7">
-        <v>0.4956586454973952</v>
+        <v>0.3181395348837209</v>
       </c>
       <c r="AJ7">
-        <v>0.289906400202378</v>
+        <v>0.1390880412962432</v>
       </c>
       <c r="AK7">
-        <v>0.3604907203523121</v>
+        <v>0.2485904664274731</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1275,7 +1323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PT BFI Finance Indonesia Tbk (IDX:BFIN)</t>
+          <t>PT Trust Finance Indonesia Tbk (IDX:TRUS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1284,10 +1332,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0803</v>
+        <v>0.0547</v>
       </c>
       <c r="E8">
-        <v>0.0864</v>
+        <v>0.0941</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1302,85 +1350,82 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>108</v>
+        <v>1.67</v>
       </c>
       <c r="L8">
-        <v>0.4395604395604396</v>
+        <v>0.4883040935672515</v>
       </c>
       <c r="M8">
-        <v>16.7</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.01652810768012668</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.1546296296296296</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>16.7</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.01652810768012668</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.1546296296296296</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>86.7</v>
+        <v>2.57</v>
       </c>
       <c r="V8">
-        <v>0.08580760095011877</v>
+        <v>0.1374331550802139</v>
       </c>
       <c r="W8">
-        <v>0.214583747268031</v>
+        <v>0.07389380530973451</v>
       </c>
       <c r="X8">
-        <v>0.06157655670521376</v>
+        <v>0.05821276397532887</v>
       </c>
       <c r="Y8">
-        <v>0.1530071905628172</v>
+        <v>0.01568104133440563</v>
       </c>
       <c r="Z8">
-        <v>0.2692307692307692</v>
+        <v>0.1873254094319987</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06357056056454763</v>
+        <v>0.05818114293688495</v>
       </c>
       <c r="AC8">
-        <v>-0.06357056056454763</v>
+        <v>-0.05818114293688495</v>
       </c>
       <c r="AD8">
-        <v>675.7</v>
+        <v>2.34</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>675.7</v>
+        <v>2.34</v>
       </c>
       <c r="AG8">
-        <v>589</v>
+        <v>-0.23</v>
       </c>
       <c r="AH8">
-        <v>0.4007472866378033</v>
+        <v>0.1112167300380228</v>
       </c>
       <c r="AI8">
-        <v>0.5448314787937429</v>
+        <v>0.08917682926829268</v>
       </c>
       <c r="AJ8">
-        <v>0.3682630986619982</v>
+        <v>-0.01245262587980509</v>
       </c>
       <c r="AK8">
-        <v>0.5106198526224534</v>
+        <v>-0.009716941275876637</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1397,7 +1442,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PT Adira Dinamika Multi Finance Tbk (IDX:ADMF)</t>
+          <t>PT Mandala Multifinance Tbk (IDX:MFIN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1406,10 +1451,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0521</v>
+        <v>0.0548</v>
       </c>
       <c r="E9">
-        <v>0.0604</v>
+        <v>0.0833</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1424,28 +1469,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>105.4</v>
+        <v>32.1</v>
       </c>
       <c r="L9">
-        <v>0.312759643916914</v>
+        <v>0.3165680473372781</v>
       </c>
       <c r="M9">
-        <v>39.9</v>
+        <v>17.1</v>
       </c>
       <c r="N9">
-        <v>0.06927083333333334</v>
+        <v>0.03399602385685885</v>
       </c>
       <c r="O9">
-        <v>0.3785578747628083</v>
+        <v>0.5327102803738318</v>
       </c>
       <c r="P9">
-        <v>39.9</v>
+        <v>17.1</v>
       </c>
       <c r="Q9">
-        <v>0.06927083333333334</v>
+        <v>0.03399602385685885</v>
       </c>
       <c r="R9">
-        <v>0.3785578747628083</v>
+        <v>0.5327102803738318</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1454,55 +1499,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>149.3</v>
+        <v>93.7</v>
       </c>
       <c r="V9">
-        <v>0.2592013888888889</v>
+        <v>0.1862823061630219</v>
       </c>
       <c r="W9">
-        <v>0.1815363417154668</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="X9">
-        <v>0.06876417835227283</v>
+        <v>0.06209243551695155</v>
       </c>
       <c r="Y9">
-        <v>0.1127721633631939</v>
+        <v>0.0958023013251537</v>
       </c>
       <c r="Z9">
-        <v>0.2534978185647661</v>
+        <v>0.3189682290028311</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06389742862538933</v>
+        <v>0.06088926943947814</v>
       </c>
       <c r="AC9">
-        <v>-0.06389742862538933</v>
+        <v>-0.06088926943947814</v>
       </c>
       <c r="AD9">
-        <v>720.6</v>
+        <v>204.4</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>720.6</v>
+        <v>204.4</v>
       </c>
       <c r="AG9">
-        <v>571.3</v>
+        <v>110.7</v>
       </c>
       <c r="AH9">
-        <v>0.5557612216566405</v>
+        <v>0.288945433983602</v>
       </c>
       <c r="AI9">
-        <v>0.5365199910654457</v>
+        <v>0.4866666666666667</v>
       </c>
       <c r="AJ9">
-        <v>0.4979517127168134</v>
+        <v>0.1803812937917549</v>
       </c>
       <c r="AK9">
-        <v>0.478555872005361</v>
+        <v>0.3392583512105424</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1519,7 +1564,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PT Radana Bhaskara Finance Tbk (IDX:HDFA)</t>
+          <t>PT Adira Dinamika Multi Finance Tbk (IDX:ADMF)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1528,7 +1573,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0003500000000000001</v>
+        <v>-0.0156</v>
+      </c>
+      <c r="E10">
+        <v>0.0155</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1543,82 +1591,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>2.51</v>
+        <v>116.5</v>
       </c>
       <c r="L10">
-        <v>0.3653566229985444</v>
+        <v>0.3159750474640629</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>51.9</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.07291373981455465</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.4454935622317596</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>51.9</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.07291373981455465</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.4454935622317596</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>3.65</v>
+        <v>119.2</v>
       </c>
       <c r="V10">
-        <v>0.05555555555555555</v>
+        <v>0.1674627704411352</v>
       </c>
       <c r="W10">
-        <v>0.06747311827956988</v>
+        <v>0.1871485943775101</v>
       </c>
       <c r="X10">
-        <v>0.06344846825396978</v>
+        <v>0.07604006904349009</v>
       </c>
       <c r="Y10">
-        <v>0.004024650025600096</v>
+        <v>0.11110852533402</v>
       </c>
       <c r="Z10">
-        <v>0.1099375900144023</v>
+        <v>0.3088457027977886</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.06484725545067302</v>
+        <v>0.06154197367195777</v>
       </c>
       <c r="AC10">
-        <v>-0.06484725545067302</v>
+        <v>-0.06154197367195777</v>
       </c>
       <c r="AD10">
-        <v>53.9</v>
+        <v>1008.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>53.9</v>
+        <v>1008.9</v>
       </c>
       <c r="AG10">
-        <v>50.25</v>
+        <v>889.6999999999999</v>
       </c>
       <c r="AH10">
-        <v>0.4506688963210703</v>
+        <v>0.5863311443017377</v>
       </c>
       <c r="AI10">
-        <v>0.5556701030927835</v>
+        <v>0.5961004431314623</v>
       </c>
       <c r="AJ10">
-        <v>0.4333764553686934</v>
+        <v>0.5555416796753043</v>
       </c>
       <c r="AK10">
-        <v>0.5382967327262989</v>
+        <v>0.5654992690523104</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1635,7 +1686,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PT KDB Tifa Finance Tbk (IDX:TIFA)</t>
+          <t>PT Woori Finance Indonesia Tbk (IDX:BPFI)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1644,10 +1695,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.103</v>
+        <v>-0.0198</v>
       </c>
       <c r="E11">
-        <v>0.203</v>
+        <v>-0.0431</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1662,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3.84</v>
+        <v>4.11</v>
       </c>
       <c r="L11">
-        <v>0.4665856622114216</v>
+        <v>0.2668831168831169</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1689,55 +1740,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>16.3</v>
+        <v>1.21</v>
       </c>
       <c r="V11">
-        <v>0.1765980498374865</v>
+        <v>0.01689944134078212</v>
       </c>
       <c r="W11">
-        <v>0.05363128491620112</v>
+        <v>0.06492890995260664</v>
       </c>
       <c r="X11">
-        <v>0.05669192902174643</v>
+        <v>0.06398150662671885</v>
       </c>
       <c r="Y11">
-        <v>-0.00306064410554531</v>
+        <v>0.0009474033258877884</v>
       </c>
       <c r="Z11">
-        <v>0.1402044293015332</v>
+        <v>0.1991207654512542</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.06928878526715473</v>
+        <v>0.06185060978166303</v>
       </c>
       <c r="AC11">
-        <v>-0.06928878526715473</v>
+        <v>-0.06185060978166303</v>
       </c>
       <c r="AD11">
-        <v>25.2</v>
+        <v>38.9</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>25.2</v>
+        <v>38.9</v>
       </c>
       <c r="AG11">
-        <v>8.899999999999999</v>
+        <v>37.69</v>
       </c>
       <c r="AH11">
-        <v>0.214468085106383</v>
+        <v>0.3520361990950226</v>
       </c>
       <c r="AI11">
-        <v>0.2619542619542619</v>
+        <v>0.3676748582230623</v>
       </c>
       <c r="AJ11">
-        <v>0.08794466403162055</v>
+        <v>0.3448622929819746</v>
       </c>
       <c r="AK11">
-        <v>0.1113892365456821</v>
+        <v>0.3603594989960799</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1754,7 +1805,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PT. Clipan Finance Indonesia Tbk (IDX:CFIN)</t>
+          <t>PT BFI Finance Indonesia Tbk (IDX:BFIN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1763,10 +1814,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.16</v>
+        <v>0.0567</v>
       </c>
       <c r="E12">
-        <v>-0.271</v>
+        <v>0.0306</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1781,82 +1832,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>3.13</v>
+        <v>108.1</v>
       </c>
       <c r="L12">
-        <v>0.1298755186721992</v>
+        <v>0.3836053938963804</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>58.3</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.04949066213921902</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.5393154486586494</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>58.3</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.04949066213921902</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.5393154486586494</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>3.14</v>
+        <v>132.9</v>
       </c>
       <c r="V12">
-        <v>0.04104575163398693</v>
+        <v>0.1128183361629881</v>
       </c>
       <c r="W12">
-        <v>0.009276822762299941</v>
+        <v>0.191496899911426</v>
       </c>
       <c r="X12">
-        <v>0.07455602755242061</v>
+        <v>0.06687524145542148</v>
       </c>
       <c r="Y12">
-        <v>-0.06527920479012067</v>
+        <v>0.1246216584560046</v>
       </c>
       <c r="Z12">
-        <v>0.0493145078780438</v>
+        <v>0.2442999566536628</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0694945455275057</v>
+        <v>0.06213770537916003</v>
       </c>
       <c r="AC12">
-        <v>-0.0694945455275057</v>
+        <v>-0.06213770537916003</v>
       </c>
       <c r="AD12">
-        <v>131.6</v>
+        <v>887.1</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>131.6</v>
+        <v>887.1</v>
       </c>
       <c r="AG12">
-        <v>128.46</v>
+        <v>754.2</v>
       </c>
       <c r="AH12">
-        <v>0.632388274867852</v>
+        <v>0.4295675754200766</v>
       </c>
       <c r="AI12">
-        <v>0.2910216718266254</v>
+        <v>0.5931795386158476</v>
       </c>
       <c r="AJ12">
-        <v>0.6267564402810305</v>
+        <v>0.3903322637408136</v>
       </c>
       <c r="AK12">
-        <v>0.2860642230436912</v>
+        <v>0.5535006605019815</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1873,7 +1927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PT Wahana Ottomitra Multiartha Tbk (IDX:WOMF)</t>
+          <t>PT Mizuho Leasing Indonesia Tbk (IDX:VRNA)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1881,12 +1935,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.0189</v>
-      </c>
-      <c r="E13">
-        <v>0.08560000000000001</v>
-      </c>
       <c r="G13">
         <v>0</v>
       </c>
@@ -1900,85 +1948,82 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>10.4</v>
+        <v>2.8</v>
       </c>
       <c r="L13">
-        <v>0.1533923303834808</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="M13">
-        <v>2.16</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.03756521739130435</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.2076923076923077</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>2.16</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.03756521739130435</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.2076923076923077</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>41.2</v>
+        <v>2.19</v>
       </c>
       <c r="V13">
-        <v>0.7165217391304348</v>
+        <v>0.06886792452830189</v>
       </c>
       <c r="W13">
-        <v>0.1152993348115299</v>
+        <v>0.06222222222222222</v>
       </c>
       <c r="X13">
-        <v>0.1068822321040607</v>
+        <v>0.1114080354178181</v>
       </c>
       <c r="Y13">
-        <v>0.008417102707469273</v>
+        <v>-0.04918581319559592</v>
       </c>
       <c r="Z13">
-        <v>0.2256990679094541</v>
+        <v>0.09054933261788181</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.07410592791926007</v>
+        <v>0.0633777453405646</v>
       </c>
       <c r="AC13">
-        <v>-0.07410592791926007</v>
+        <v>-0.0633777453405646</v>
       </c>
       <c r="AD13">
-        <v>249.5</v>
+        <v>126.6</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>249.5</v>
+        <v>126.6</v>
       </c>
       <c r="AG13">
-        <v>208.3</v>
+        <v>124.41</v>
       </c>
       <c r="AH13">
-        <v>0.8127035830618893</v>
+        <v>0.7992424242424242</v>
       </c>
       <c r="AI13">
-        <v>0.7265579499126383</v>
+        <v>0.7271682940838599</v>
       </c>
       <c r="AJ13">
-        <v>0.7836719337848006</v>
+        <v>0.7964278855386978</v>
       </c>
       <c r="AK13">
-        <v>0.6892786234281932</v>
+        <v>0.7236926298644639</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -1995,7 +2040,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PT Mizuho Leasing Indonesia Tbk (IDX:VRNA)</t>
+          <t>PT. Clipan Finance Indonesia Tbk (IDX:CFIN)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2004,10 +2049,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.218</v>
+        <v>-0.0145</v>
       </c>
       <c r="E14">
-        <v>0.352</v>
+        <v>0.261</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2022,82 +2067,85 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>2.2</v>
+        <v>61.6</v>
       </c>
       <c r="L14">
-        <v>0.1189189189189189</v>
+        <v>0.8966521106259098</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>25.8</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.2033096926713948</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0.4188311688311688</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>25.8</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.2033096926713948</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0.4188311688311688</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>4.31</v>
+        <v>2.47</v>
       </c>
       <c r="V14">
-        <v>0.1149333333333333</v>
+        <v>0.01946414499605989</v>
       </c>
       <c r="W14">
-        <v>0.04782608695652174</v>
+        <v>0.1921397379912664</v>
       </c>
       <c r="X14">
-        <v>0.08900301168118203</v>
+        <v>0.08163140359589638</v>
       </c>
       <c r="Y14">
-        <v>-0.04117692472466029</v>
+        <v>0.11050833439537</v>
       </c>
       <c r="Z14">
-        <v>0.1199429460580913</v>
+        <v>0.152986237919209</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.07472248852405076</v>
+        <v>0.0649814334294939</v>
       </c>
       <c r="AC14">
-        <v>-0.07472248852405076</v>
+        <v>-0.0649814334294939</v>
       </c>
       <c r="AD14">
-        <v>108.4</v>
+        <v>231.3</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>108.4</v>
+        <v>231.3</v>
       </c>
       <c r="AG14">
-        <v>104.09</v>
+        <v>228.83</v>
       </c>
       <c r="AH14">
-        <v>0.7429746401644962</v>
+        <v>0.6457286432160804</v>
       </c>
       <c r="AI14">
-        <v>0.7066492829204694</v>
+        <v>0.3972179289026276</v>
       </c>
       <c r="AJ14">
-        <v>0.7351507874849919</v>
+        <v>0.643268771259101</v>
       </c>
       <c r="AK14">
-        <v>0.6981688912737273</v>
+        <v>0.3946501560802304</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2123,10 +2171,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.00843</v>
+        <v>0.0594</v>
       </c>
       <c r="E15">
-        <v>-0.00235</v>
+        <v>0.157</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2141,28 +2189,28 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>4.45</v>
+        <v>6.85</v>
       </c>
       <c r="L15">
-        <v>0.2170731707317073</v>
+        <v>0.2762096774193548</v>
       </c>
       <c r="M15">
-        <v>0.648</v>
+        <v>1.63</v>
       </c>
       <c r="N15">
-        <v>0.01007776049766719</v>
+        <v>0.02308781869688385</v>
       </c>
       <c r="O15">
-        <v>0.1456179775280899</v>
+        <v>0.2379562043795621</v>
       </c>
       <c r="P15">
-        <v>0.648</v>
+        <v>1.63</v>
       </c>
       <c r="Q15">
-        <v>0.01007776049766719</v>
+        <v>0.02308781869688385</v>
       </c>
       <c r="R15">
-        <v>0.1456179775280899</v>
+        <v>0.2379562043795621</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2171,55 +2219,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>25.4</v>
+        <v>33.5</v>
       </c>
       <c r="V15">
-        <v>0.3950233281493001</v>
+        <v>0.4745042492917848</v>
       </c>
       <c r="W15">
-        <v>0.05186480186480187</v>
+        <v>0.08125741399762752</v>
       </c>
       <c r="X15">
-        <v>0.08902799318186769</v>
+        <v>0.1061774995567704</v>
       </c>
       <c r="Y15">
-        <v>-0.03716319131706582</v>
+        <v>-0.02492008555914291</v>
       </c>
       <c r="Z15">
-        <v>0.09018917729872415</v>
+        <v>0.1012658227848101</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.07472633759905567</v>
+        <v>0.06678340467654571</v>
       </c>
       <c r="AC15">
-        <v>-0.07472633759905567</v>
+        <v>-0.06678340467654571</v>
       </c>
       <c r="AD15">
-        <v>186</v>
+        <v>254.3</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>186</v>
+        <v>254.3</v>
       </c>
       <c r="AG15">
-        <v>160.6</v>
+        <v>220.8</v>
       </c>
       <c r="AH15">
-        <v>0.7431082700759088</v>
+        <v>0.7827023699599878</v>
       </c>
       <c r="AI15">
-        <v>0.6881243063263041</v>
+        <v>0.7437847323778883</v>
       </c>
       <c r="AJ15">
-        <v>0.7140951534015119</v>
+        <v>0.7577213452299246</v>
       </c>
       <c r="AK15">
-        <v>0.6557778685177624</v>
+        <v>0.7159533073929962</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2236,121 +2284,698 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>PT Wahana Ottomitra Multiartha Tbk (IDX:WOMF)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>-0.0198</v>
+      </c>
+      <c r="E16">
+        <v>-0.0142</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>14</v>
+      </c>
+      <c r="L16">
+        <v>0.1861702127659574</v>
+      </c>
+      <c r="M16">
+        <v>3.8</v>
+      </c>
+      <c r="N16">
+        <v>0.04611650485436893</v>
+      </c>
+      <c r="O16">
+        <v>0.2714285714285714</v>
+      </c>
+      <c r="P16">
+        <v>3.8</v>
+      </c>
+      <c r="Q16">
+        <v>0.04611650485436893</v>
+      </c>
+      <c r="R16">
+        <v>0.2714285714285714</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>35</v>
+      </c>
+      <c r="V16">
+        <v>0.424757281553398</v>
+      </c>
+      <c r="W16">
+        <v>0.1490947816826411</v>
+      </c>
+      <c r="X16">
+        <v>0.1067796446927983</v>
+      </c>
+      <c r="Y16">
+        <v>0.04231513698984284</v>
+      </c>
+      <c r="Z16">
+        <v>0.2488418266048974</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.06681026343006854</v>
+      </c>
+      <c r="AC16">
+        <v>-0.06681026343006854</v>
+      </c>
+      <c r="AD16">
+        <v>300.4</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>300.4</v>
+      </c>
+      <c r="AG16">
+        <v>265.4</v>
+      </c>
+      <c r="AH16">
+        <v>0.7847439916405434</v>
+      </c>
+      <c r="AI16">
+        <v>0.7443012884043607</v>
+      </c>
+      <c r="AJ16">
+        <v>0.7630822311673375</v>
+      </c>
+      <c r="AK16">
+        <v>0.7200217037438958</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PT Radana Bhaskara Finance Tbk (IDX:HDFA)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>-0.145</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1.74</v>
+      </c>
+      <c r="L17">
+        <v>0.2636363636363637</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>-0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>3.51</v>
+      </c>
+      <c r="V17">
+        <v>0.08258823529411764</v>
+      </c>
+      <c r="W17">
+        <v>0.04037122969837587</v>
+      </c>
+      <c r="X17">
+        <v>0.08852441424184437</v>
+      </c>
+      <c r="Y17">
+        <v>-0.04815318454346851</v>
+      </c>
+      <c r="Z17">
+        <v>0.07070166041778254</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.06713757164573174</v>
+      </c>
+      <c r="AC17">
+        <v>-0.06713757164573174</v>
+      </c>
+      <c r="AD17">
+        <v>98.7</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>98.7</v>
+      </c>
+      <c r="AG17">
+        <v>95.19</v>
+      </c>
+      <c r="AH17">
+        <v>0.6990084985835695</v>
+      </c>
+      <c r="AI17">
+        <v>0.6902097902097902</v>
+      </c>
+      <c r="AJ17">
+        <v>0.6913356089766868</v>
+      </c>
+      <c r="AK17">
+        <v>0.6824145100007168</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PT Venteny Fortuna International Tbk (IDX:VTNY)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0.379</v>
+      </c>
+      <c r="L18">
+        <v>0.0554904831625183</v>
+      </c>
+      <c r="M18">
+        <v>-0</v>
+      </c>
+      <c r="N18">
+        <v>-0</v>
+      </c>
+      <c r="O18">
+        <v>-0</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>-0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>12.2</v>
+      </c>
+      <c r="V18">
+        <v>0.08513607815771108</v>
+      </c>
+      <c r="W18">
+        <v>0.07097378277153558</v>
+      </c>
+      <c r="X18">
+        <v>0.05957674721712766</v>
+      </c>
+      <c r="Y18">
+        <v>0.01139703555440792</v>
+      </c>
+      <c r="Z18">
+        <v>0.3309108527131783</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.06932112454579063</v>
+      </c>
+      <c r="AC18">
+        <v>-0.06932112454579063</v>
+      </c>
+      <c r="AD18">
+        <v>32.1</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>32.1</v>
+      </c>
+      <c r="AG18">
+        <v>19.9</v>
+      </c>
+      <c r="AH18">
+        <v>0.1830102622576967</v>
+      </c>
+      <c r="AI18">
+        <v>0.5449915110356536</v>
+      </c>
+      <c r="AJ18">
+        <v>0.1219362745098039</v>
+      </c>
+      <c r="AK18">
+        <v>0.4261241970021413</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>PT Indomobil Multi Jasa Tbk (IDX:IMJS)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.106</v>
-      </c>
-      <c r="E16">
-        <v>-0.06519999999999999</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>6.64</v>
-      </c>
-      <c r="L16">
-        <v>0.02346289752650177</v>
-      </c>
-      <c r="M16">
-        <v>0.142</v>
-      </c>
-      <c r="N16">
-        <v>0.0008114285714285713</v>
-      </c>
-      <c r="O16">
-        <v>0.0213855421686747</v>
-      </c>
-      <c r="P16">
-        <v>0.142</v>
-      </c>
-      <c r="Q16">
-        <v>0.0008114285714285713</v>
-      </c>
-      <c r="R16">
-        <v>0.0213855421686747</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="V16">
-        <v>0.4862857142857143</v>
-      </c>
-      <c r="W16">
-        <v>0.02665596146126054</v>
-      </c>
-      <c r="X16">
-        <v>0.1461314255941585</v>
-      </c>
-      <c r="Y16">
-        <v>-0.1194754641328979</v>
-      </c>
-      <c r="Z16">
-        <v>0.1860006572461387</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0.07589380010060834</v>
-      </c>
-      <c r="AC16">
-        <v>-0.07589380010060834</v>
-      </c>
-      <c r="AD16">
-        <v>1315.8</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>1315.8</v>
-      </c>
-      <c r="AG16">
-        <v>1230.7</v>
-      </c>
-      <c r="AH16">
-        <v>0.8826133619533136</v>
-      </c>
-      <c r="AI16">
-        <v>0.8308916393028543</v>
-      </c>
-      <c r="AJ16">
-        <v>0.8755068649071637</v>
-      </c>
-      <c r="AK16">
-        <v>0.821287954621288</v>
-      </c>
-      <c r="AL16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>-1.17</v>
-      </c>
-      <c r="AQ16">
-        <v>-0</v>
+      <c r="D19">
+        <v>0.09210000000000002</v>
+      </c>
+      <c r="E19">
+        <v>-0.123</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>7.64</v>
+      </c>
+      <c r="L19">
+        <v>0.02622725712324064</v>
+      </c>
+      <c r="M19">
+        <v>0.28</v>
+      </c>
+      <c r="N19">
+        <v>0.001777777777777778</v>
+      </c>
+      <c r="O19">
+        <v>0.03664921465968587</v>
+      </c>
+      <c r="P19">
+        <v>0.28</v>
+      </c>
+      <c r="Q19">
+        <v>0.001777777777777778</v>
+      </c>
+      <c r="R19">
+        <v>0.03664921465968587</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>94.3</v>
+      </c>
+      <c r="V19">
+        <v>0.5987301587301587</v>
+      </c>
+      <c r="W19">
+        <v>0.03071974266184158</v>
+      </c>
+      <c r="X19">
+        <v>0.1852528727401818</v>
+      </c>
+      <c r="Y19">
+        <v>-0.1545331300783403</v>
+      </c>
+      <c r="Z19">
+        <v>0.1969041503312154</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.07024940667004094</v>
+      </c>
+      <c r="AC19">
+        <v>-0.07024940667004094</v>
+      </c>
+      <c r="AD19">
+        <v>1470.1</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>1470.1</v>
+      </c>
+      <c r="AG19">
+        <v>1375.8</v>
+      </c>
+      <c r="AH19">
+        <v>0.9032317522732858</v>
+      </c>
+      <c r="AI19">
+        <v>0.8368531906415438</v>
+      </c>
+      <c r="AJ19">
+        <v>0.8972803756603405</v>
+      </c>
+      <c r="AK19">
+        <v>0.8275986525505293</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-2.03</v>
+      </c>
+      <c r="AQ19">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PT Intan Baru Prana Tbk (IDX:IBFN)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K20">
+        <v>-4.39</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>3.99</v>
+      </c>
+      <c r="V20">
+        <v>2.241573033707865</v>
+      </c>
+      <c r="W20">
+        <v>0.12296918767507</v>
+      </c>
+      <c r="X20">
+        <v>0.5478528710035622</v>
+      </c>
+      <c r="Y20">
+        <v>-0.4248836833284921</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.0713077863870084</v>
+      </c>
+      <c r="AC20">
+        <v>-0.0713077863870084</v>
+      </c>
+      <c r="AD20">
+        <v>63.4</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>63.4</v>
+      </c>
+      <c r="AG20">
+        <v>59.41</v>
+      </c>
+      <c r="AH20">
+        <v>0.9726910095121204</v>
+      </c>
+      <c r="AI20">
+        <v>2.697872340425532</v>
+      </c>
+      <c r="AJ20">
+        <v>0.9709102794574277</v>
+      </c>
+      <c r="AK20">
+        <v>3.045105074320861</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-0.082</v>
+      </c>
+      <c r="AQ20">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PT Cashlez Worldwide Indonesia Tbk (IDX:CASH)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>-0.0272</v>
+      </c>
+      <c r="H21">
+        <v>-0.0272</v>
+      </c>
+      <c r="I21">
+        <v>-0.02608</v>
+      </c>
+      <c r="J21">
+        <v>-0.02608</v>
+      </c>
+      <c r="K21">
+        <v>-0.453</v>
+      </c>
+      <c r="L21">
+        <v>-0.03624</v>
+      </c>
+      <c r="M21">
+        <v>-0</v>
+      </c>
+      <c r="N21">
+        <v>-0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>1.24</v>
+      </c>
+      <c r="V21">
+        <v>0.1215686274509804</v>
+      </c>
+      <c r="W21">
+        <v>-0.07677966101694915</v>
+      </c>
+      <c r="X21">
+        <v>0.05866400584837418</v>
+      </c>
+      <c r="Y21">
+        <v>-0.1354436668653233</v>
+      </c>
+      <c r="Z21">
+        <v>6.151574803149606</v>
+      </c>
+      <c r="AA21">
+        <v>-0.1604330708661417</v>
+      </c>
+      <c r="AB21">
+        <v>0.0585637303923585</v>
+      </c>
+      <c r="AC21">
+        <v>-0.2189968012585002</v>
+      </c>
+      <c r="AD21">
+        <v>1.61</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>1.61</v>
+      </c>
+      <c r="AG21">
+        <v>0.3700000000000001</v>
+      </c>
+      <c r="AH21">
+        <v>0.1363251481795089</v>
+      </c>
+      <c r="AI21">
+        <v>0.1191709844559586</v>
+      </c>
+      <c r="AJ21">
+        <v>0.03500473036896879</v>
+      </c>
+      <c r="AK21">
+        <v>0.03015484922575388</v>
+      </c>
+      <c r="AL21">
+        <v>0.077</v>
+      </c>
+      <c r="AM21">
+        <v>0.077</v>
+      </c>
+      <c r="AN21">
+        <v>-24.02985074626866</v>
+      </c>
+      <c r="AO21">
+        <v>-4.233766233766234</v>
+      </c>
+      <c r="AP21">
+        <v>-5.522388059701494</v>
+      </c>
+      <c r="AQ21">
+        <v>-4.233766233766234</v>
       </c>
     </row>
   </sheetData>
